--- a/教師.xlsx
+++ b/教師.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\MyWeb\CourseSystem\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC5761EA-C4B9-4508-ADEA-84EFF4A55868}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B406DC-882E-41A1-B033-E4C4D52BC13D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{774E8F57-B7B9-4829-A8DB-7F71255F457E}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{774E8F57-B7B9-4829-A8DB-7F71255F457E}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="94">
   <si>
     <t>蘇泓俊</t>
   </si>
@@ -274,7 +274,21 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>英文</t>
+    <t>國語文;閱讀;數學;健康;校本走讀;科園大小事;生活;藝術(美勞);綜合活動;玩轉魔數;自主學習</t>
+  </si>
+  <si>
+    <t>閱讀;健康;社會</t>
+  </si>
+  <si>
+    <t>藝術(音樂);閱讀;健康</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然科學;健康;閱讀</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>資智通鑑;自然科學;健康</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -282,27 +296,72 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>體育</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>自然</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>藝(音)</t>
-  </si>
-  <si>
-    <t>彈(資)</t>
-  </si>
-  <si>
-    <t>社會;健康</t>
-  </si>
-  <si>
-    <t>藝(音);健康;閱</t>
-  </si>
-  <si>
-    <t>彈(資);健康;社會</t>
+    <t>資智通鑑;社會;健康;藝術(美勞)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>體育;健康</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>藝術(音樂)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>閱讀;健康;社會;體育</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英語文;國際移動力</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>社會;健康;閱讀</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>英語文;國際移動力;健康;閱讀</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>T041</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>鐘點</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然鐘點</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本土_閩語1</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本土_閩語2</t>
+  </si>
+  <si>
+    <t>本土_客語</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>本土語文</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>自然科學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>T042</t>
+  </si>
+  <si>
+    <t>T043</t>
+  </si>
+  <si>
+    <t>T044</t>
   </si>
 </sst>
 </file>
@@ -524,7 +583,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -569,6 +628,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -904,198 +969,213 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC1C179B-FCA6-4155-8585-6C5877205B1F}">
-  <dimension ref="A1:F31"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F35"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14" style="16" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="9" style="16"/>
+    <col min="6" max="6" width="87.375" style="16" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="15" t="s">
         <v>32</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="15" t="s">
         <v>33</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>40</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="15">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E2" s="15"/>
+      <c r="F2" s="15" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>41</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="15">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E3" s="15"/>
+      <c r="F3" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="15">
         <v>3</v>
       </c>
-      <c r="F4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E4" s="15"/>
+      <c r="F4" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C5" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="15">
         <v>3</v>
       </c>
-      <c r="F5" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E5" s="15"/>
+      <c r="F5" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="15">
         <v>9</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E6" s="15"/>
+      <c r="F6" s="15" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="7" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>58</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="15">
         <v>9</v>
       </c>
-      <c r="F7" t="s">
+      <c r="E7" s="15"/>
+      <c r="F7" s="15" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="15">
         <v>9</v>
       </c>
-      <c r="F8" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E8" s="15"/>
+      <c r="F8" s="15" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>59</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="15">
         <v>9</v>
       </c>
-      <c r="F9" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
+      <c r="E9" s="15"/>
+      <c r="F9" s="15" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="15" t="s">
         <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C10" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="15">
         <v>9</v>
       </c>
-      <c r="F10" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
+      <c r="E10" s="15"/>
+      <c r="F10" s="15" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="15" t="s">
         <v>46</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C11" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="15">
         <v>9</v>
       </c>
-      <c r="F11" t="s">
-        <v>72</v>
+      <c r="E11" s="15"/>
+      <c r="F11" s="15" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1105,150 +1185,175 @@
       <c r="B12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C12" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="15">
         <v>9</v>
       </c>
-      <c r="F12" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="E12" s="15"/>
+      <c r="F12" s="15" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="15" t="s">
         <v>55</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C13" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="15">
         <v>16</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="15">
         <v>101</v>
       </c>
+      <c r="F13" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="14" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
+      <c r="A14" s="15" t="s">
         <v>56</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C14" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="15">
         <v>16</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="15">
         <v>102</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F14" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>61</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C15" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="15">
         <v>16</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="15">
         <v>201</v>
       </c>
+      <c r="F15" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="16" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" t="s">
+      <c r="A16" s="15" t="s">
         <v>52</v>
       </c>
       <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C16" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="15">
         <v>16</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="15">
         <v>202</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F16" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>62</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="C17" t="s">
+      <c r="C17" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="15">
         <v>16</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="15">
         <v>301</v>
       </c>
+      <c r="F17" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="18" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" t="s">
+      <c r="A18" s="15" t="s">
         <v>54</v>
       </c>
       <c r="B18" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="15">
         <v>16</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="15">
         <v>302</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="F18" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="15" t="s">
         <v>50</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C19" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="15">
         <v>16</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="15">
         <v>401</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
         <v>63</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C20" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="15">
         <v>16</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="15">
         <v>402</v>
+      </c>
+      <c r="F20" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1258,99 +1363,117 @@
       <c r="B21" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C21" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="15">
         <v>16</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="15">
         <v>403</v>
       </c>
-    </row>
-    <row r="22" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
+      <c r="F21" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="15" t="s">
         <v>57</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C22" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D22">
+      <c r="D22" s="15">
         <v>16</v>
       </c>
-      <c r="E22">
+      <c r="E22" s="15">
         <v>501</v>
       </c>
-    </row>
-    <row r="23" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F22" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="8" t="s">
         <v>65</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D23">
+      <c r="D23" s="15">
         <v>16</v>
       </c>
-      <c r="E23">
+      <c r="E23" s="15">
         <v>502</v>
       </c>
+      <c r="F23" t="s">
+        <v>70</v>
+      </c>
     </row>
     <row r="24" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" t="s">
+      <c r="A24" s="15" t="s">
         <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C24" t="s">
+      <c r="C24" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D24">
+      <c r="D24" s="15">
         <v>16</v>
       </c>
-      <c r="E24">
+      <c r="E24" s="15">
         <v>503</v>
       </c>
-    </row>
-    <row r="25" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="F24" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>66</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C25" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D25">
+      <c r="D25" s="15">
         <v>16</v>
       </c>
-      <c r="E25">
+      <c r="E25" s="15">
         <v>601</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
+      <c r="F25" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
         <v>53</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C26" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D26">
+      <c r="D26" s="15">
         <v>16</v>
       </c>
-      <c r="E26">
+      <c r="E26" s="15">
         <v>602</v>
+      </c>
+      <c r="F26" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1360,65 +1483,71 @@
       <c r="B27" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C27" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="D27">
+      <c r="D27" s="15">
         <v>16</v>
       </c>
-      <c r="E27">
+      <c r="E27" s="15">
         <v>603</v>
       </c>
-    </row>
-    <row r="28" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
+      <c r="F27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
         <v>48</v>
       </c>
       <c r="B28" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C28" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D28">
+      <c r="D28" s="15">
         <v>19</v>
       </c>
-      <c r="F28" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+      <c r="E28" s="15"/>
+      <c r="F28" s="15" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="15" t="s">
         <v>51</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D29">
+      <c r="D29" s="15">
         <v>20</v>
       </c>
-      <c r="F29" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="18.75" x14ac:dyDescent="0.25">
+      <c r="E29" s="15"/>
+      <c r="F29" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
         <v>68</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D30">
+      <c r="D30" s="15">
         <v>20</v>
       </c>
-      <c r="F30" t="s">
-        <v>71</v>
+      <c r="E30" s="15"/>
+      <c r="F30" s="15" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="31" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
@@ -1428,14 +1557,71 @@
       <c r="B31" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C31" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="D31">
+      <c r="D31" s="15">
         <v>20</v>
       </c>
-      <c r="F31" t="s">
-        <v>70</v>
+      <c r="E31" s="15"/>
+      <c r="F31" s="15" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>86</v>
+      </c>
+      <c r="C32" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F32" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F33" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="C34" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C35" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
